--- a/backend-train-model/person-train-model/train-docs/new_person_labels_人工分组记录表模板.xlsx
+++ b/backend-train-model/person-train-model/train-docs/new_person_labels_人工分组记录表模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University-Competition\Innovation_Entrepreneurship\MyProgram\yolov8-program\backend-train-model\person-train-model\train-docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\University-Competition\Innovation_Entrepreneurship\MyProgram\yolov8-program\backend-train-model\person-train-model\train-docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{923349CC-5216-4BFA-85CF-3077AE584C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6ECE1C2-54F3-473B-A1B6-0D27A6BCB3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" xr2:uid="{74626489-A8B0-4605-B49F-88CD1DEDA5FD}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12561" activeTab="1" xr2:uid="{74626489-A8B0-4605-B49F-88CD1DEDA5FD}"/>
   </bookViews>
   <sheets>
     <sheet name="填写说明" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="110">
   <si>
     <t>模块</t>
   </si>
@@ -119,136 +119,270 @@
     <t>人工组名称/场景名</t>
   </si>
   <si>
+    <t>场景编号/区域名</t>
+  </si>
+  <si>
+    <t>视角编号</t>
+  </si>
+  <si>
+    <t>稳定性等级：A/B/C</t>
+  </si>
+  <si>
+    <t>组级ROI/逐图ROI/暂缓</t>
+  </si>
+  <si>
+    <t>是否可共用一版ROI</t>
+  </si>
+  <si>
+    <t>是否需要继续细拆</t>
+  </si>
+  <si>
+    <t>继续细拆依据（如白天/夜晚/远近景）</t>
+  </si>
+  <si>
+    <t>代表帧文件名</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>未开始/进行中/已确认</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>group_0001</t>
+  </si>
+  <si>
+    <t>1280x720</t>
+  </si>
+  <si>
+    <t>group_0002</t>
+  </si>
+  <si>
+    <t>1920x1080</t>
+  </si>
+  <si>
+    <t>group_0003</t>
+  </si>
+  <si>
+    <t>group_0004</t>
+  </si>
+  <si>
+    <t>group_0005</t>
+  </si>
+  <si>
+    <t>图片stem（不含扩展名）</t>
+  </si>
+  <si>
+    <t>图片文件名</t>
+  </si>
+  <si>
+    <t>自动粗分组ID</t>
+  </si>
+  <si>
+    <t>人工最终组ID</t>
+  </si>
+  <si>
+    <t>摄像头编号</t>
+  </si>
+  <si>
+    <t>白天/夜晚</t>
+  </si>
+  <si>
+    <t>近景/远景</t>
+  </si>
+  <si>
+    <t>左偏/右偏/居中</t>
+  </si>
+  <si>
+    <t>是否疑似标注问题</t>
+  </si>
+  <si>
+    <t>保留/细拆/逐图ROI/暂缓</t>
+  </si>
+  <si>
+    <t>示例：00231</t>
+  </si>
+  <si>
+    <t>00231.jpg</t>
+  </si>
+  <si>
+    <t>待人工填写</t>
+  </si>
+  <si>
+    <t>人工组名称</t>
+  </si>
+  <si>
+    <t>group / per_image</t>
+  </si>
+  <si>
+    <t>ROI工作目录</t>
+  </si>
+  <si>
+    <t>组内图片目录</t>
+  </si>
+  <si>
+    <t>组内标签目录</t>
+  </si>
+  <si>
+    <t>ROI JSON 输出目录</t>
+  </si>
+  <si>
+    <t>建议代表帧数量</t>
+  </si>
+  <si>
+    <t>建议抽检数量</t>
+  </si>
+  <si>
+    <t>未开始/进行中/已完成</t>
+  </si>
+  <si>
+    <t>标注负责人</t>
+  </si>
+  <si>
+    <t>计划完成日期</t>
+  </si>
+  <si>
     <t>摄像头编号（未知可留空）</t>
-  </si>
-  <si>
-    <t>场景编号/区域名</t>
-  </si>
-  <si>
-    <t>视角编号</t>
-  </si>
-  <si>
-    <t>稳定性等级：A/B/C</t>
-  </si>
-  <si>
-    <t>组级ROI/逐图ROI/暂缓</t>
-  </si>
-  <si>
-    <t>是否可共用一版ROI</t>
-  </si>
-  <si>
-    <t>是否需要继续细拆</t>
-  </si>
-  <si>
-    <t>继续细拆依据（如白天/夜晚/远近景）</t>
-  </si>
-  <si>
-    <t>代表帧文件名</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>未开始/进行中/已确认</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>group_0001</t>
-  </si>
-  <si>
-    <t>1280x720</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>group_0002</t>
-  </si>
-  <si>
-    <t>1920x1080</t>
-  </si>
-  <si>
-    <t>group_0003</t>
-  </si>
-  <si>
-    <t>group_0004</t>
-  </si>
-  <si>
-    <t>group_0005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>组级ROI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>否</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李含昱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>group_0006</t>
-  </si>
-  <si>
-    <t>图片stem（不含扩展名）</t>
-  </si>
-  <si>
-    <t>图片文件名</t>
-  </si>
-  <si>
-    <t>自动粗分组ID</t>
-  </si>
-  <si>
-    <t>人工最终组ID</t>
-  </si>
-  <si>
-    <t>摄像头编号</t>
-  </si>
-  <si>
-    <t>白天/夜晚</t>
-  </si>
-  <si>
-    <t>近景/远景</t>
-  </si>
-  <si>
-    <t>左偏/右偏/居中</t>
-  </si>
-  <si>
-    <t>是否疑似标注问题</t>
-  </si>
-  <si>
-    <t>保留/细拆/逐图ROI/暂缓</t>
-  </si>
-  <si>
-    <t>示例：00231</t>
-  </si>
-  <si>
-    <t>00231.jpg</t>
-  </si>
-  <si>
-    <t>待人工填写</t>
-  </si>
-  <si>
-    <t>人工组名称</t>
-  </si>
-  <si>
-    <t>group / per_image</t>
-  </si>
-  <si>
-    <t>ROI工作目录</t>
-  </si>
-  <si>
-    <t>组内图片目录</t>
-  </si>
-  <si>
-    <t>组内标签目录</t>
-  </si>
-  <si>
-    <t>ROI JSON 输出目录</t>
-  </si>
-  <si>
-    <t>建议代表帧数量</t>
-  </si>
-  <si>
-    <t>建议抽检数量</t>
-  </si>
-  <si>
-    <t>未开始/进行中/已完成</t>
-  </si>
-  <si>
-    <t>标注负责人</t>
-  </si>
-  <si>
-    <t>计划完成日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>田相利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>高鑫锐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>未开始</t>
+  </si>
+  <si>
+    <t>李含昱</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>粗略ROI第一版；使用现有代表帧进行组级ROI标注；按静态工作区口径画ROI。</t>
+  </si>
+  <si>
+    <t>高鑫锐</t>
+  </si>
+  <si>
+    <t>田相利</t>
+  </si>
+  <si>
+    <t>group_0006</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0001/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0001/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0001/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0001/roi-json</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0002/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0002/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0002/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0002/roi-json</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0003/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0003/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0003/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0003/roi-json</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0004/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0004/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0004/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0004/roi-json</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0005/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0005/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0005/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0005/roi-json</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0006/roi-work</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0006/images</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0006/labels</t>
+  </si>
+  <si>
+    <t>backend-train-model/person-train-model/train-result/working/new_person_labels_frames_grouping_t006/grouped/group_0006/roi-json</t>
   </si>
 </sst>
 </file>
@@ -309,12 +443,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -665,7 +805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="264.39999999999998" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="27.85" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -748,135 +888,268 @@
   <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="3"/>
+    <col min="7" max="8" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="3"/>
+    <col min="10" max="10" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="3"/>
+    <col min="15" max="15" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="6.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="55.7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" ht="55.7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="3">
+        <v>272</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B2">
-        <v>272</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
+      <c r="D2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="3">
+        <v>449</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B3">
-        <v>449</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="3">
+        <v>127</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4">
-        <v>127</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="3">
+        <v>387</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B5">
-        <v>387</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>582</v>
       </c>
-      <c r="C6" t="s">
-        <v>40</v>
+      <c r="C6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7">
+      <c r="A7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="3">
         <v>690</v>
       </c>
-      <c r="C7" t="s">
-        <v>40</v>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -903,60 +1176,60 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="55.7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -967,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E403A0CF-BE26-4617-ACF9-0F7489AA38CD}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="13.95" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -980,43 +1253,289 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="41.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
